--- a/Auto event script.xlsx
+++ b/Auto event script.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FE\lt-maker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CBBE459-A7BF-42C7-9BD1-6111AD9DA679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7199364F-8700-4E42-870E-3B2F99813A1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{8E0F047B-701A-4951-B23D-E04F5C53C7C1}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="40">
   <si>
     <t>NAME</t>
   </si>
@@ -132,9 +132,6 @@
     <t>Brigand</t>
   </si>
   <si>
-    <t>Hard</t>
-  </si>
-  <si>
     <t>modify</t>
   </si>
   <si>
@@ -181,6 +178,9 @@
   </si>
   <si>
     <t>Set stat</t>
+  </si>
+  <si>
+    <t>Nightmare</t>
   </si>
 </sst>
 </file>
@@ -637,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0145414-02B0-4CEF-B4A4-1E3158EA1D48}">
-  <dimension ref="A1:AE25"/>
+  <dimension ref="A1:AE35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="13" max="13" width="19.109375" bestFit="1" customWidth="1"/>
@@ -702,16 +702,16 @@
         <v>12</v>
       </c>
       <c r="N1" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="O1" s="8" t="s">
-        <v>39</v>
-      </c>
       <c r="P1" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S1" s="9" t="str" cm="1">
-        <f t="array" ref="S1:AE12">_xlfn._xlws.FILTER(A1:M25, A1:A25&lt;&gt;"")</f>
+        <f t="array" ref="S1:AE19">_xlfn._xlws.FILTER(A1:M35, A1:A35&lt;&gt;"")</f>
         <v>NAME</v>
       </c>
       <c r="T1" s="9" t="str">
@@ -789,22 +789,22 @@
         <v>7</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="O2" s="9" t="str">
-        <f>"set_stats;" &amp; $N$2 &amp; "_" &amp; (ROW(A1)-1) &amp; ";HP," &amp; V2 &amp; ",STR," &amp; W2 &amp; ",MAG," &amp; X2 &amp; ",SKL," &amp; Y2 &amp; ",SPD," &amp; Z2 &amp; ",LCK," &amp; AA2 &amp; ",DEF," &amp; AB2 &amp; ",RES," &amp; AC2 &amp; ";immediate"</f>
-        <v>set_stats;Hard_0;HP,24,STR,6,MAG,0,SKL,11,SPD,9,LCK,0,DEF,6,RES,0;immediate</v>
+        <f>"    set_stats;" &amp; $N$2 &amp; "_" &amp; (ROW(A1)-1) &amp; ";HP," &amp; V2 &amp; ",STR," &amp; W2 &amp; ",MAG," &amp; X2 &amp; ",SKL," &amp; Y2 &amp; ",SPD," &amp; Z2 &amp; ",LCK," &amp; AA2 &amp; ",DEF," &amp; AB2 &amp; ",RES," &amp; AC2 &amp; ";immediate"</f>
+        <v xml:space="preserve">    set_stats;Nightmare_0;HP,24,STR,6,MAG,0,SKL,11,SPD,9,LCK,0,DEF,6,RES,0;immediate</v>
       </c>
       <c r="P2" s="9" t="str">
-        <f>IFERROR("modify_item_component;" &amp; $N$2 &amp; "_" &amp; (ROW(A1)-1) &amp; ";" &amp; SUBSTITUTE(TRIM(LEFT(AE2, FIND("(", AE2)-1)), " ", "_") &amp; ";" &amp; IF(ISNUMBER(SEARCH("mighty", AE2)), "damage", IF(ISNUMBER(SEARCH("mt", AE2)), "damage", IF(ISNUMBER(SEARCH("hit", AE2)), "hit", IF(ISNUMBER(SEARCH("crit", AE2)), "crit", IF(ISNUMBER(SEARCH("weight", AE2)), "weight", IF(ISNUMBER(SEARCH("wt", AE2)), "weight", "")))))) &amp; ";" &amp; TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(MID(AE2, FIND("(", AE2) + 1, FIND(")", AE2) - FIND("(", AE2) - 1)), "mighty", ""), "mt", ""), "hit", ""), "crit", ""), "weight", ""), "wt", ""), "+", "")) &amp; ";additive", "")</f>
-        <v>modify_item_component;Hard_0;Steel_Sword;damage;3;additive</v>
+        <f>IFERROR("    modify_item_component;" &amp; $N$2 &amp; "_" &amp; (ROW(A1)-1) &amp; ";" &amp; SUBSTITUTE(TRIM(LEFT(AE2, FIND("(", AE2)-1)), " ", "_") &amp; ";" &amp; IF(ISNUMBER(SEARCH("mighty", AE2)), "damage", IF(ISNUMBER(SEARCH("mt", AE2)), "damage", IF(ISNUMBER(SEARCH("hit", AE2)), "hit", IF(ISNUMBER(SEARCH("crit", AE2)), "crit", IF(ISNUMBER(SEARCH("weight", AE2)), "weight", IF(ISNUMBER(SEARCH("wt", AE2)), "weight", "")))))) &amp; ";" &amp; TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(MID(AE2, FIND("(", AE2) + 1, FIND(")", AE2) - FIND("(", AE2) - 1)), "mighty", ""), "mt", ""), "hit", ""), "crit", ""), "weight", ""), "wt", ""), "+", "")) &amp; ";additive", "")</f>
+        <v xml:space="preserve">    modify_item_component;Nightmare_0;Steel_Sword;damage;3;additive</v>
       </c>
       <c r="Q2" s="9" t="str">
-        <f>IF(P2&lt;&gt;"", "change_item_name;" &amp; $N$2 &amp; "_" &amp; (ROW(A1)-1) &amp; ";" &amp; SUBSTITUTE(TRIM(LEFT(AE2&amp;"(", FIND("(", AE2&amp;"(")-1)), " ", "_") &amp; ";&lt;moreblue&gt;" &amp; TRIM(LEFT(AE2&amp;"(", FIND("(", AE2&amp;"(")-1)), "")</f>
-        <v>change_item_name;Hard_0;Steel_Sword;&lt;moreblue&gt;Steel Sword</v>
+        <f>IF(P2&lt;&gt;"", "    change_item_name;" &amp; $N$2 &amp; "_" &amp; (ROW(A1)-1) &amp; ";" &amp; SUBSTITUTE(TRIM(LEFT(AE2&amp;"(", FIND("(", AE2&amp;"(")-1)), " ", "_") &amp; ";&lt;moreblue&gt;" &amp; TRIM(LEFT(AE2&amp;"(", FIND("(", AE2&amp;"(")-1)), "")</f>
+        <v xml:space="preserve">    change_item_name;Nightmare_0;Steel_Sword;&lt;moreblue&gt;Steel Sword</v>
       </c>
       <c r="S2" s="9" t="str">
         <v>Bandit</v>
@@ -860,15 +860,19 @@
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
       <c r="M3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+      <c r="O3" s="9" t="str">
+        <f t="shared" ref="O3:O29" si="0">"    set_stats;" &amp; $N$2 &amp; "_" &amp; (ROW(A2)-1) &amp; ";HP," &amp; V3 &amp; ",STR," &amp; W3 &amp; ",MAG," &amp; X3 &amp; ",SKL," &amp; Y3 &amp; ",SPD," &amp; Z3 &amp; ",LCK," &amp; AA3 &amp; ",DEF," &amp; AB3 &amp; ",RES," &amp; AC3 &amp; ";immediate"</f>
+        <v xml:space="preserve">    set_stats;Nightmare_1;HP,20,STR,8,MAG,2,SKL,8,SPD,9,LCK,1,DEF,8,RES,4;immediate</v>
       </c>
       <c r="P3" s="9" t="str">
-        <f t="shared" ref="P3:P11" si="0">IFERROR("modify_item_component;" &amp; $N$2 &amp; "_" &amp; (ROW(A2)-1) &amp; ";" &amp; SUBSTITUTE(TRIM(LEFT(AE3, FIND("(", AE3)-1)), " ", "_") &amp; ";" &amp; IF(ISNUMBER(SEARCH("mighty", AE3)), "damage", IF(ISNUMBER(SEARCH("mt", AE3)), "damage", IF(ISNUMBER(SEARCH("hit", AE3)), "hit", IF(ISNUMBER(SEARCH("crit", AE3)), "crit", IF(ISNUMBER(SEARCH("weight", AE3)), "weight", IF(ISNUMBER(SEARCH("wt", AE3)), "weight", "")))))) &amp; ";" &amp; TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(MID(AE3, FIND("(", AE3) + 1, FIND(")", AE3) - FIND("(", AE3) - 1)), "mighty", ""), "mt", ""), "hit", ""), "crit", ""), "weight", ""), "wt", ""), "+", "")) &amp; ";additive", "")</f>
-        <v>modify_item_component;Hard_1;Steel_Lance;damage;3;additive</v>
+        <f t="shared" ref="P3:P28" si="1">IFERROR("    modify_item_component;" &amp; $N$2 &amp; "_" &amp; (ROW(A2)-1) &amp; ";" &amp; SUBSTITUTE(TRIM(LEFT(AE3, FIND("(", AE3)-1)), " ", "_") &amp; ";" &amp; IF(ISNUMBER(SEARCH("mighty", AE3)), "damage", IF(ISNUMBER(SEARCH("mt", AE3)), "damage", IF(ISNUMBER(SEARCH("hit", AE3)), "hit", IF(ISNUMBER(SEARCH("crit", AE3)), "crit", IF(ISNUMBER(SEARCH("weight", AE3)), "weight", IF(ISNUMBER(SEARCH("wt", AE3)), "weight", "")))))) &amp; ";" &amp; TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(MID(AE3, FIND("(", AE3) + 1, FIND(")", AE3) - FIND("(", AE3) - 1)), "mighty", ""), "mt", ""), "hit", ""), "crit", ""), "weight", ""), "wt", ""), "+", "")) &amp; ";additive", "")</f>
+        <v xml:space="preserve">    modify_item_component;Nightmare_1;Steel_Lance;damage;3;additive</v>
       </c>
       <c r="Q3" s="9" t="str">
-        <f t="shared" ref="Q3:Q12" si="1">IF(P3&lt;&gt;"", "change_item_name;" &amp; $N$2 &amp; "_" &amp; (ROW(A2)-1) &amp; ";" &amp; SUBSTITUTE(TRIM(LEFT(AE3&amp;"(", FIND("(", AE3&amp;"(")-1)), " ", "_") &amp; ";&lt;moreblue&gt;" &amp; TRIM(LEFT(AE3&amp;"(", FIND("(", AE3&amp;"(")-1)), "")</f>
-        <v>change_item_name;Hard_1;Steel_Lance;&lt;moreblue&gt;Steel Lance</v>
+        <f t="shared" ref="Q3:Q16" si="2">IF(P3&lt;&gt;"", "    change_item_name;" &amp; $N$2 &amp; "_" &amp; (ROW(A2)-1) &amp; ";" &amp; SUBSTITUTE(TRIM(LEFT(AE3&amp;"(", FIND("(", AE3&amp;"(")-1)), " ", "_") &amp; ";&lt;moreblue&gt;" &amp; TRIM(LEFT(AE3&amp;"(", FIND("(", AE3&amp;"(")-1)), "")</f>
+        <v xml:space="preserve">    change_item_name;Nightmare_1;Steel_Lance;&lt;moreblue&gt;Steel Lance</v>
       </c>
       <c r="S3" s="9" t="str">
         <v>Bandit</v>
@@ -948,15 +952,19 @@
         <v>5</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="O4" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_2;HP,19,STR,8,MAG,0,SKL,6,SPD,6,LCK,2,DEF,6,RES,4;immediate</v>
       </c>
       <c r="P4" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>modify_item_component;Hard_2;Steel_Bow;damage;3;additive</v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    modify_item_component;Nightmare_2;Steel_Bow;damage;3;additive</v>
       </c>
       <c r="Q4" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>change_item_name;Hard_2;Steel_Bow;&lt;moreblue&gt;Steel Bow</v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">    change_item_name;Nightmare_2;Steel_Bow;&lt;moreblue&gt;Steel Bow</v>
       </c>
       <c r="S4" s="9" t="str">
         <v>Bandit</v>
@@ -1012,15 +1020,19 @@
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
       <c r="M5" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="O5" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_3;HP,28,STR,9,MAG,0,SKL,8,SPD,8,LCK,5,DEF,7,RES,3;immediate</v>
       </c>
       <c r="P5" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>modify_item_component;Hard_3;Steel_Axe;damage;3;additive</v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">    modify_item_component;Nightmare_3;Steel_Axe;damage;3;additive</v>
       </c>
       <c r="Q5" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>change_item_name;Hard_3;Steel_Axe;&lt;moreblue&gt;Steel Axe</v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">    change_item_name;Nightmare_3;Steel_Axe;&lt;moreblue&gt;Steel Axe</v>
       </c>
       <c r="S5" s="9" t="str">
         <v>Bandit</v>
@@ -1100,14 +1112,18 @@
         <v>5</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="O6" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_4;HP,22,STR,6,MAG,1,SKL,8,SPD,8,LCK,0,DEF,6,RES,1;immediate</v>
       </c>
       <c r="P6" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="Q6" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S6" s="9" t="str">
@@ -1164,14 +1180,18 @@
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
       <c r="M7" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="O7" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_5;HP,19,STR,6,MAG,0,SKL,8,SPD,8,LCK,2,DEF,6,RES,4;immediate</v>
       </c>
       <c r="P7" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="Q7" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S7" s="9" t="str">
@@ -1252,14 +1272,18 @@
         <v>5</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="O8" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_6;HP,18,STR,9,MAG,0,SKL,3,SPD,5,LCK,1,DEF,4,RES,3;immediate</v>
       </c>
       <c r="P8" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="Q8" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S8" s="9" t="str">
@@ -1316,14 +1340,18 @@
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
       <c r="M9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
+      </c>
+      <c r="O9" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_7;HP,26,STR,9,MAG,0,SKL,8,SPD,7,LCK,4,DEF,6,RES,3;immediate</v>
       </c>
       <c r="P9" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="Q9" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S9" s="9" t="str">
@@ -1404,14 +1432,18 @@
         <v>7</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="O10" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_8;HP,29,STR,10,MAG,2,SKL,8,SPD,10,LCK,2,DEF,7,RES,1;immediate</v>
       </c>
       <c r="P10" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="Q10" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S10" s="9" t="str">
@@ -1454,7 +1486,7 @@
         <v>Steel Axe</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -1470,12 +1502,16 @@
       <c r="M11" s="4" t="s">
         <v>19</v>
       </c>
+      <c r="O11" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_9;HP,29,STR,11,MAG,1,SKL,8,SPD,10,LCK,2,DEF,7,RES,1;immediate</v>
+      </c>
       <c r="P11" s="9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="Q11" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S11" s="9" t="str">
@@ -1532,14 +1568,18 @@
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+      <c r="O12" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_10;HP,29,STR,11,MAG,0,SKL,8,SPD,10,LCK,2,DEF,7,RES,2;immediate</v>
       </c>
       <c r="P12" s="9" t="str">
-        <f>IFERROR("modify_item_component;" &amp; $N$2 &amp; "_" &amp; (ROW(A11)-1) &amp; ";" &amp; SUBSTITUTE(TRIM(LEFT(AE12, FIND("(", AE12)-1)), " ", "_") &amp; ";" &amp; IF(ISNUMBER(SEARCH("mighty", AE12)), "damage", IF(ISNUMBER(SEARCH("mt", AE12)), "damage", IF(ISNUMBER(SEARCH("hit", AE12)), "hit", IF(ISNUMBER(SEARCH("crit", AE12)), "crit", IF(ISNUMBER(SEARCH("weight", AE12)), "weight", IF(ISNUMBER(SEARCH("wt", AE12)), "weight", "")))))) &amp; ";" &amp; TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(MID(AE12, FIND("(", AE12) + 1, FIND(")", AE12) - FIND("(", AE12) - 1)), "mighty", ""), "mt", ""), "hit", ""), "crit", ""), "weight", ""), "wt", ""), "+", "")) &amp; ";additive", "")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="Q12" s="9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S12" s="9" t="str">
@@ -1620,7 +1660,58 @@
         <v>5</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="O13" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_11;HP,29,STR,11,MAG,1,SKL,8,SPD,10,LCK,2,DEF,7,RES,2;immediate</v>
+      </c>
+      <c r="P13" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q13" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="S13" s="9" t="str">
+        <v>Bandit</v>
+      </c>
+      <c r="T13" s="9" t="str">
+        <v>Brigand</v>
+      </c>
+      <c r="U13" s="9">
+        <v>3</v>
+      </c>
+      <c r="V13" s="9">
+        <v>29</v>
+      </c>
+      <c r="W13" s="9">
+        <v>11</v>
+      </c>
+      <c r="X13" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>8</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>10</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>2</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>7</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>2</v>
+      </c>
+      <c r="AD13" s="9">
+        <v>5</v>
+      </c>
+      <c r="AE13" s="9" t="str">
+        <v>Steel Axe</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.3">
@@ -1639,6 +1730,57 @@
       <c r="M14" s="4" t="s">
         <v>20</v>
       </c>
+      <c r="O14" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_12;HP,29,STR,11,MAG,0,SKL,8,SPD,10,LCK,2,DEF,7,RES,2;immediate</v>
+      </c>
+      <c r="P14" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q14" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="S14" s="9" t="str">
+        <v>Bandit</v>
+      </c>
+      <c r="T14" s="9" t="str">
+        <v>Brigand</v>
+      </c>
+      <c r="U14" s="9">
+        <v>3</v>
+      </c>
+      <c r="V14" s="9">
+        <v>29</v>
+      </c>
+      <c r="W14" s="9">
+        <v>11</v>
+      </c>
+      <c r="X14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="9">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="9">
+        <v>10</v>
+      </c>
+      <c r="AA14" s="9">
+        <v>2</v>
+      </c>
+      <c r="AB14" s="9">
+        <v>7</v>
+      </c>
+      <c r="AC14" s="9">
+        <v>2</v>
+      </c>
+      <c r="AD14" s="9">
+        <v>5</v>
+      </c>
+      <c r="AE14" s="9" t="str">
+        <v>Steel Axe</v>
+      </c>
     </row>
     <row r="15" spans="1:31" ht="41.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6"/>
@@ -1654,7 +1796,58 @@
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
       <c r="M15" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="O15" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_13;HP,27,STR,9,MAG,0,SKL,6,SPD,8,LCK,1,DEF,5,RES,1;immediate</v>
+      </c>
+      <c r="P15" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q15" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="S15" s="9" t="str">
+        <v>Bandit</v>
+      </c>
+      <c r="T15" s="9" t="str">
+        <v>Brigand</v>
+      </c>
+      <c r="U15" s="9">
+        <v>2</v>
+      </c>
+      <c r="V15" s="9">
+        <v>27</v>
+      </c>
+      <c r="W15" s="9">
+        <v>9</v>
+      </c>
+      <c r="X15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="9">
+        <v>6</v>
+      </c>
+      <c r="Z15" s="9">
+        <v>8</v>
+      </c>
+      <c r="AA15" s="9">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="9">
+        <v>5</v>
+      </c>
+      <c r="AC15" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="9">
+        <v>5</v>
+      </c>
+      <c r="AE15" s="9" t="str">
+        <v>Steel Axe</v>
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.3">
@@ -1695,10 +1888,61 @@
         <v>5</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="O16" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_14;HP,27,STR,10,MAG,0,SKL,6,SPD,8,LCK,1,DEF,5,RES,0;immediate</v>
+      </c>
+      <c r="P16" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q16" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="S16" s="9" t="str">
+        <v>Bandit</v>
+      </c>
+      <c r="T16" s="9" t="str">
+        <v>Brigand</v>
+      </c>
+      <c r="U16" s="9">
+        <v>2</v>
+      </c>
+      <c r="V16" s="9">
+        <v>27</v>
+      </c>
+      <c r="W16" s="9">
+        <v>10</v>
+      </c>
+      <c r="X16" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="9">
+        <v>6</v>
+      </c>
+      <c r="Z16" s="9">
+        <v>8</v>
+      </c>
+      <c r="AA16" s="9">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="9">
+        <v>5</v>
+      </c>
+      <c r="AC16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="9">
+        <v>5</v>
+      </c>
+      <c r="AE16" s="9" t="str">
+        <v>Steel Axe</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1714,8 +1958,59 @@
       <c r="M17" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O17" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_15;HP,27,STR,10,MAG,1,SKL,6,SPD,8,LCK,1,DEF,5,RES,1;immediate</v>
+      </c>
+      <c r="P17" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q17" s="9" t="str">
+        <f t="shared" ref="Q3:Q29" si="3">IF(P17&lt;&gt;"", "change_item_name;" &amp; $N$2 &amp; "_" &amp; (ROW(A16)-1) &amp; ";" &amp; SUBSTITUTE(TRIM(LEFT(AE17&amp;"(", FIND("(", AE17&amp;"(")-1)), " ", "_") &amp; ";&lt;moreblue&gt;" &amp; TRIM(LEFT(AE17&amp;"(", FIND("(", AE17&amp;"(")-1)), "")</f>
+        <v/>
+      </c>
+      <c r="S17" s="9" t="str">
+        <v>Bandit</v>
+      </c>
+      <c r="T17" s="9" t="str">
+        <v>Brigand</v>
+      </c>
+      <c r="U17" s="9">
+        <v>2</v>
+      </c>
+      <c r="V17" s="9">
+        <v>27</v>
+      </c>
+      <c r="W17" s="9">
+        <v>10</v>
+      </c>
+      <c r="X17" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="9">
+        <v>6</v>
+      </c>
+      <c r="Z17" s="9">
+        <v>8</v>
+      </c>
+      <c r="AA17" s="9">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="9">
+        <v>5</v>
+      </c>
+      <c r="AC17" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="9">
+        <v>5</v>
+      </c>
+      <c r="AE17" s="9" t="str">
+        <v>Steel Axe</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -1729,10 +2024,61 @@
       <c r="K18" s="6"/>
       <c r="L18" s="6"/>
       <c r="M18" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="O18" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_16;HP,27,STR,10,MAG,0,SKL,6,SPD,8,LCK,1,DEF,5,RES,1;immediate</v>
+      </c>
+      <c r="P18" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q18" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S18" s="9" t="str">
+        <v>Bandit</v>
+      </c>
+      <c r="T18" s="9" t="str">
+        <v>Brigand</v>
+      </c>
+      <c r="U18" s="9">
+        <v>2</v>
+      </c>
+      <c r="V18" s="9">
+        <v>27</v>
+      </c>
+      <c r="W18" s="9">
+        <v>10</v>
+      </c>
+      <c r="X18" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="9">
+        <v>6</v>
+      </c>
+      <c r="Z18" s="9">
+        <v>8</v>
+      </c>
+      <c r="AA18" s="9">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="9">
+        <v>5</v>
+      </c>
+      <c r="AC18" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD18" s="9">
+        <v>5</v>
+      </c>
+      <c r="AE18" s="9" t="str">
+        <v>Steel Axe</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>13</v>
       </c>
@@ -1770,10 +2116,61 @@
         <v>5</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+      <c r="O19" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_17;HP,27,STR,10,MAG,0,SKL,6,SPD,8,LCK,1,DEF,5,RES,1;immediate</v>
+      </c>
+      <c r="P19" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q19" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="S19" s="9" t="str">
+        <v>Bandit</v>
+      </c>
+      <c r="T19" s="9" t="str">
+        <v>Brigand</v>
+      </c>
+      <c r="U19" s="9">
+        <v>2</v>
+      </c>
+      <c r="V19" s="9">
+        <v>27</v>
+      </c>
+      <c r="W19" s="9">
+        <v>10</v>
+      </c>
+      <c r="X19" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="9">
+        <v>6</v>
+      </c>
+      <c r="Z19" s="9">
+        <v>8</v>
+      </c>
+      <c r="AA19" s="9">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="9">
+        <v>5</v>
+      </c>
+      <c r="AC19" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="9">
+        <v>5</v>
+      </c>
+      <c r="AE19" s="9" t="str">
+        <v>Steel Axe</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -1787,10 +2184,22 @@
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
       <c r="M20" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="O20" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_18;HP,,STR,,MAG,,SKL,,SPD,,LCK,,DEF,,RES,;immediate</v>
+      </c>
+      <c r="P20" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q20" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>13</v>
       </c>
@@ -1828,10 +2237,22 @@
         <v>5</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+      <c r="O21" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_19;HP,,STR,,MAG,,SKL,,SPD,,LCK,,DEF,,RES,;immediate</v>
+      </c>
+      <c r="P21" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q21" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:31" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -1845,10 +2266,22 @@
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
       <c r="M22" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+      <c r="O22" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_20;HP,,STR,,MAG,,SKL,,SPD,,LCK,,DEF,,RES,;immediate</v>
+      </c>
+      <c r="P22" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q22" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>13</v>
       </c>
@@ -1886,10 +2319,22 @@
         <v>5</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+      <c r="O23" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_21;HP,,STR,,MAG,,SKL,,SPD,,LCK,,DEF,,RES,;immediate</v>
+      </c>
+      <c r="P23" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q23" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:31" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -1903,52 +2348,498 @@
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
       <c r="M24" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O24" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_22;HP,,STR,,MAG,,SKL,,SPD,,LCK,,DEF,,RES,;immediate</v>
+      </c>
+      <c r="P24" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q24" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="5">
         <v>3</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" s="5">
         <v>29</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" s="5">
         <v>11</v>
       </c>
-      <c r="F25" s="1">
-        <v>0</v>
-      </c>
-      <c r="G25" s="1">
-        <v>8</v>
-      </c>
-      <c r="H25" s="1">
+      <c r="F25" s="5">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5">
+        <v>8</v>
+      </c>
+      <c r="H25" s="5">
         <v>10</v>
       </c>
-      <c r="I25" s="1">
-        <v>2</v>
-      </c>
-      <c r="J25" s="1">
+      <c r="I25" s="5">
+        <v>2</v>
+      </c>
+      <c r="J25" s="5">
         <v>7</v>
       </c>
-      <c r="K25" s="1">
-        <v>2</v>
-      </c>
-      <c r="L25" s="1">
-        <v>5</v>
-      </c>
-      <c r="M25" s="1" t="s">
+      <c r="K25" s="5">
+        <v>2</v>
+      </c>
+      <c r="L25" s="5">
+        <v>5</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O25" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_23;HP,,STR,,MAG,,SKL,,SPD,,LCK,,DEF,,RES,;immediate</v>
+      </c>
+      <c r="P25" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q25" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:31" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="3" t="s">
         <v>36</v>
       </c>
+      <c r="O26" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_24;HP,,STR,,MAG,,SKL,,SPD,,LCK,,DEF,,RES,;immediate</v>
+      </c>
+      <c r="P26" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q26" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="5">
+        <v>3</v>
+      </c>
+      <c r="D27" s="5">
+        <v>29</v>
+      </c>
+      <c r="E27" s="5">
+        <v>11</v>
+      </c>
+      <c r="F27" s="5">
+        <v>1</v>
+      </c>
+      <c r="G27" s="5">
+        <v>8</v>
+      </c>
+      <c r="H27" s="5">
+        <v>10</v>
+      </c>
+      <c r="I27" s="5">
+        <v>2</v>
+      </c>
+      <c r="J27" s="5">
+        <v>7</v>
+      </c>
+      <c r="K27" s="5">
+        <v>2</v>
+      </c>
+      <c r="L27" s="5">
+        <v>5</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O27" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_25;HP,,STR,,MAG,,SKL,,SPD,,LCK,,DEF,,RES,;immediate</v>
+      </c>
+      <c r="P27" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q27" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:31" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="O28" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_26;HP,,STR,,MAG,,SKL,,SPD,,LCK,,DEF,,RES,;immediate</v>
+      </c>
+      <c r="P28" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q28" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="5">
+        <v>3</v>
+      </c>
+      <c r="D29" s="5">
+        <v>29</v>
+      </c>
+      <c r="E29" s="5">
+        <v>11</v>
+      </c>
+      <c r="F29" s="5">
+        <v>0</v>
+      </c>
+      <c r="G29" s="5">
+        <v>8</v>
+      </c>
+      <c r="H29" s="5">
+        <v>10</v>
+      </c>
+      <c r="I29" s="5">
+        <v>2</v>
+      </c>
+      <c r="J29" s="5">
+        <v>7</v>
+      </c>
+      <c r="K29" s="5">
+        <v>2</v>
+      </c>
+      <c r="L29" s="5">
+        <v>5</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O29" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    set_stats;Nightmare_27;HP,,STR,,MAG,,SKL,,SPD,,LCK,,DEF,,RES,;immediate</v>
+      </c>
+      <c r="P29" s="9" t="str">
+        <f t="shared" ref="P3:P29" si="4">IFERROR("modify_item_component;" &amp; $N$2 &amp; "_" &amp; (ROW(A28)-1) &amp; ";" &amp; SUBSTITUTE(TRIM(LEFT(AE29, FIND("(", AE29)-1)), " ", "_") &amp; ";" &amp; IF(ISNUMBER(SEARCH("mighty", AE29)), "damage", IF(ISNUMBER(SEARCH("mt", AE29)), "damage", IF(ISNUMBER(SEARCH("hit", AE29)), "hit", IF(ISNUMBER(SEARCH("crit", AE29)), "crit", IF(ISNUMBER(SEARCH("weight", AE29)), "weight", IF(ISNUMBER(SEARCH("wt", AE29)), "weight", "")))))) &amp; ";" &amp; TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(LOWER(MID(AE29, FIND("(", AE29) + 1, FIND(")", AE29) - FIND("(", AE29) - 1)), "mighty", ""), "mt", ""), "hit", ""), "crit", ""), "weight", ""), "wt", ""), "+", "")) &amp; ";additive", "")</f>
+        <v/>
+      </c>
+      <c r="Q29" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:31" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2</v>
+      </c>
+      <c r="D31" s="1">
+        <v>27</v>
+      </c>
+      <c r="E31" s="1">
+        <v>9</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>6</v>
+      </c>
+      <c r="H31" s="1">
+        <v>8</v>
+      </c>
+      <c r="I31" s="1">
+        <v>1</v>
+      </c>
+      <c r="J31" s="1">
+        <v>5</v>
+      </c>
+      <c r="K31" s="1">
+        <v>1</v>
+      </c>
+      <c r="L31" s="1">
+        <v>5</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2</v>
+      </c>
+      <c r="D32" s="1">
+        <v>27</v>
+      </c>
+      <c r="E32" s="1">
+        <v>10</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
+        <v>6</v>
+      </c>
+      <c r="H32" s="1">
+        <v>8</v>
+      </c>
+      <c r="I32" s="1">
+        <v>1</v>
+      </c>
+      <c r="J32" s="1">
+        <v>5</v>
+      </c>
+      <c r="K32" s="1">
+        <v>0</v>
+      </c>
+      <c r="L32" s="1">
+        <v>5</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2</v>
+      </c>
+      <c r="D33" s="1">
+        <v>27</v>
+      </c>
+      <c r="E33" s="1">
+        <v>10</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1">
+        <v>6</v>
+      </c>
+      <c r="H33" s="1">
+        <v>8</v>
+      </c>
+      <c r="I33" s="1">
+        <v>1</v>
+      </c>
+      <c r="J33" s="1">
+        <v>5</v>
+      </c>
+      <c r="K33" s="1">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1">
+        <v>5</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="1">
+        <v>2</v>
+      </c>
+      <c r="D34" s="1">
+        <v>27</v>
+      </c>
+      <c r="E34" s="1">
+        <v>10</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1">
+        <v>6</v>
+      </c>
+      <c r="H34" s="1">
+        <v>8</v>
+      </c>
+      <c r="I34" s="1">
+        <v>1</v>
+      </c>
+      <c r="J34" s="1">
+        <v>5</v>
+      </c>
+      <c r="K34" s="1">
+        <v>1</v>
+      </c>
+      <c r="L34" s="1">
+        <v>5</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2</v>
+      </c>
+      <c r="D35" s="1">
+        <v>27</v>
+      </c>
+      <c r="E35" s="1">
+        <v>10</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1">
+        <v>6</v>
+      </c>
+      <c r="H35" s="1">
+        <v>8</v>
+      </c>
+      <c r="I35" s="1">
+        <v>1</v>
+      </c>
+      <c r="J35" s="1">
+        <v>5</v>
+      </c>
+      <c r="K35" s="1">
+        <v>1</v>
+      </c>
+      <c r="L35" s="1">
+        <v>5</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="120">
+  <mergeCells count="156">
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="L29:L30"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="K27:K28"/>
+    <mergeCell ref="L27:L28"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F25:F26"/>
     <mergeCell ref="G23:G24"/>
     <mergeCell ref="H23:H24"/>
     <mergeCell ref="I23:I24"/>
